--- a/notes_ccf_Semestre2_ProgrammationInformatique_Section01_G02.xlsx
+++ b/notes_ccf_Semestre2_ProgrammationInformatique_Section01_G02.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YOU-BER\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YOU-BER\Desktop\M1 french\grades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A9C6D08-DB1D-4FD0-A27C-ED83FC4DB84B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF28BD60-251F-4687-B539-A0C741C3559D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="note" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="117">
   <si>
     <t>Matricule</t>
   </si>
@@ -950,7 +950,7 @@
         <v>33</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>

--- a/notes_ccf_Semestre2_ProgrammationInformatique_Section01_G02.xlsx
+++ b/notes_ccf_Semestre2_ProgrammationInformatique_Section01_G02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YOU-BER\Desktop\M1 french\grades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF28BD60-251F-4687-B539-A0C741C3559D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B57037-E3A2-4687-A370-D892C40C93F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1028,7 +1028,7 @@
         <v>42</v>
       </c>
       <c r="D12">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1415,7 +1415,7 @@
         <v>86</v>
       </c>
       <c r="D27">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
@@ -1493,7 +1493,7 @@
         <v>95</v>
       </c>
       <c r="D30">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
